--- a/human_resources_forms/022_workplace_conflict_mediator_referral_form--human_resources_forms.xlsx
+++ b/human_resources_forms/022_workplace_conflict_mediator_referral_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'human_resources'}</t>
+          <t>human_resources</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Human Resources'}</t>
+          <t>Human Resources</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'management'}</t>
+          <t>management</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Management'}</t>
+          <t>Management</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'performance'}</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Performance'}</t>
+          <t>Performance</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'personal'}</t>
+          <t>personal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Personal'}</t>
+          <t>Personal</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'non-manager'}</t>
+          <t>non-manager</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Non-Manager'}</t>
+          <t>Non-Manager</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'retired'}</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Retired'}</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'minor'}</t>
+          <t>minor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Minor'}</t>
+          <t>Minor</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'severe'}</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Severe'}</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'success'}</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Success'}</t>
+          <t>Success</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'partial_success'}</t>
+          <t>partial_success</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Partial Success'}</t>
+          <t>Partial Success</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_a_month'}</t>
+          <t>less_than_a_month</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less than a month'}</t>
+          <t>Less than a month</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'1-3_months'}</t>
+          <t>1-3_months</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '1-3 months'}</t>
+          <t>1-3 months</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'3-6_months'}</t>
+          <t>3-6_months</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '3-6 months'}</t>
+          <t>3-6 months</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'6+_months'}</t>
+          <t>6+_months</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '6+ months'}</t>
+          <t>6+ months</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'single_incident'}</t>
+          <t>single_incident</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Single Incident'}</t>
+          <t>Single Incident</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'recurring'}</t>
+          <t>recurring</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Recurring'}</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'communication_issues'}</t>
+          <t>communication_issues</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Communication Issues'}</t>
+          <t>Communication Issues</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'trust_issues'}</t>
+          <t>trust_issues</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Trust Issues'}</t>
+          <t>Trust Issues</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'performance_issues'}</t>
+          <t>performance_issues</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Performance Issues'}</t>
+          <t>Performance Issues</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'individual_coaching'}</t>
+          <t>individual_coaching</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Individual Coaching'}</t>
+          <t>Individual Coaching</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'team_coaching'}</t>
+          <t>team_coaching</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Team Coaching'}</t>
+          <t>Team Coaching</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'human_resources'}</t>
+          <t>human_resources</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Human Resources'}</t>
+          <t>Human Resources</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1764,12 +1764,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1798,12 +1798,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
